--- a/BO4/dataset_BO4_rules.xlsx
+++ b/BO4/dataset_BO4_rules.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules_BO4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rules_BO4" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -509,7 +509,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R_JORT_001</t>
+          <t>R_VT_001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -519,17 +519,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>موافقة رئاسية على عمليات الدومين</t>
+          <t>التسجيل الرسمي لعقد البيع</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نقل أو تفويت في أملاك الدولة دون موافقة رئاسية</t>
+          <t>بيع عقار بدون تسجيل لدى قباضة التسجيل</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>مرسوم رئاسي 2026-6/7/8 — JORT N°3 يناير 2026</t>
+          <t>قانون التسجيل / مجلة الحقوق العينية الفصل 305</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بطلان العقد + عقوبات جزائية</t>
+          <t>لا قيمة قانونية — غير نافذ في مواجهة الغير</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -563,27 +563,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R_BCT_001</t>
+          <t>R_GEN_002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>بيع عقاري</t>
+          <t>عام</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ترخيص BCT للاستثمار الأجنبي</t>
+          <t>توقيع جميع الأطراف</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>معاملة عقارية بالعملة الأجنبية دون ترخيص BCT</t>
+          <t>غياب إمضاء أحد الأطراف</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>قانون الصرف n°77-608 / قانون الاستثمار 2019-47</t>
+          <t>م.ع.ع الفصل 472</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>عقوبات جزائية BCT / تجميد الأموال</t>
+          <t>بطلان العقد</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -617,27 +617,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R_GEN_002</t>
+          <t>R_BCT_001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>عام</t>
+          <t>بيع عقاري</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>توقيع جميع الأطراف</t>
+          <t>ترخيص BCT للاستثمار الأجنبي</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>غياب إمضاء أحد الأطراف</t>
+          <t>معاملة عقارية بالعملة الأجنبية دون ترخيص BCT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 472</t>
+          <t>قانون الصرف n°77-608 / قانون الاستثمار 2019-47</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -645,7 +645,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بطلان العقد</t>
+          <t>عقوبات جزائية BCT / تجميد الأموال</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -725,7 +725,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R_VT_001</t>
+          <t>R_JORT_001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -735,17 +735,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>التسجيل الرسمي لعقد البيع</t>
+          <t>موافقة رئاسية على عمليات الدومين</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>بيع عقار بدون تسجيل لدى قباضة التسجيل</t>
+          <t>نقل أو تفويت في أملاك الدولة دون موافقة رئاسية</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>قانون التسجيل / مجلة الحقوق العينية الفصل 305</t>
+          <t>مرسوم رئاسي 2026-6/7/8 — JORT N°3 يناير 2026</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>لا قيمة قانونية — غير نافذ في مواجهة الغير</t>
+          <t>بطلان العقد + عقوبات جزائية</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -833,27 +833,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R_WD_001</t>
+          <t>R_VT_002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>وعد بالبيع</t>
+          <t>بيع عقاري</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>تحديد أجل إنجاز البيع النهائي</t>
+          <t>إثبات خلو العقار من الرهن</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>غياب أجل محدد لإبرام البيع النهائي</t>
+          <t>غياب شرط خلو العقار من الرهون والاختصاصات</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 580</t>
+          <t>م.ع.ع الفصل 612 / مجلة الحقوق العينية الفصل 161</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>وعد غير ملزم — خطر التراجع</t>
+          <t>خطر الاستحقاق — إلغاء البيع</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -887,27 +887,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R_VT_005</t>
+          <t>R_WD_001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>بيع عقاري</t>
+          <t>وعد بالبيع</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>التحقق من الرسم العقاري</t>
+          <t>تحديد أجل إنجاز البيع النهائي</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>بيع عقار بدون ذكر رقم الرسم العقاري</t>
+          <t>غياب أجل محدد لإبرام البيع النهائي</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>مجلة الحقوق العينية الفصل 305</t>
+          <t>م.ع.ع الفصل 580</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -915,7 +915,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>خطر ازدواجية البيع</t>
+          <t>وعد غير ملزم — خطر التراجع</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -941,27 +941,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R_VT_002</t>
+          <t>R_KR_002</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>بيع عقاري</t>
+          <t>كراء</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>إثبات خلو العقار من الرهن</t>
+          <t>تحديد مقدار الكراء</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>غياب شرط خلو العقار من الرهون والاختصاصات</t>
+          <t>غياب المبلغ في عقد الكراء</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 612 / مجلة الحقوق العينية الفصل 161</t>
+          <t>م.ع.ع الفصل 756</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -969,7 +969,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>خطر الاستحقاق — إلغاء البيع</t>
+          <t>بطلان العقد</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -980,11 +980,11 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ÉLEVÉ</t>
+          <t>CRITIQUE</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -995,27 +995,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R_KR_002</t>
+          <t>R_VT_005</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>كراء</t>
+          <t>بيع عقاري</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>تحديد مقدار الكراء</t>
+          <t>التحقق من الرسم العقاري</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>غياب المبلغ في عقد الكراء</t>
+          <t>بيع عقار بدون ذكر رقم الرسم العقاري</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 756</t>
+          <t>مجلة الحقوق العينية الفصل 305</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بطلان العقد</t>
+          <t>خطر ازدواجية البيع</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1034,11 +1034,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>CRITIQUE</t>
+          <t>ÉLEVÉ</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1157,27 +1157,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R_VT_003</t>
+          <t>R_WK_002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>بيع عقاري</t>
+          <t>وكالة</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>حضور الشهود عند إمضاء عقد البيع</t>
+          <t>تحديد شروط إلغاء الوكالة</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>غياب الشهود في عقد البيع العقاري</t>
+          <t>غياب شروط إلغاء الوكالة</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 472</t>
+          <t>م.ع.ع الفصل 1163</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>قابلية الطعن في صحة العقد</t>
+          <t>صعوبة إلغاء الوكالة قانونياً</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1211,27 +1211,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R_WD_003</t>
+          <t>R_GEN_001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>وعد بالبيع</t>
+          <t>عام</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>تحديد قيمة العربون وشروط استرجاعه</t>
+          <t>تحديد هوية الأطراف بالكامل</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>غياب شروط استرجاع العربون</t>
+          <t>غياب أو نقص في تعريف أطراف العقد</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 439-441</t>
+          <t>م.ع.ع الفصل 2</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>نزاع حول العربون عند التراجع</t>
+          <t>قابلية الطعن في صحة العقد</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1265,27 +1265,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R_WK_002</t>
+          <t>R_GEN_003</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>وكالة</t>
+          <t>عام</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>تحديد شروط إلغاء الوكالة</t>
+          <t>تحديد موضوع العقد بوضوح</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>غياب شروط إلغاء الوكالة</t>
+          <t>موضوع العقد غامض أو ناقص</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 1163</t>
+          <t>م.ع.ع الفصل 5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>صعوبة إلغاء الوكالة قانونياً</t>
+          <t>بطلان — موضوع مجهول</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1319,27 +1319,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R_GEN_001</t>
+          <t>R_VT_003</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>عام</t>
+          <t>بيع عقاري</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>تحديد هوية الأطراف بالكامل</t>
+          <t>حضور الشهود عند إمضاء عقد البيع</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>غياب أو نقص في تعريف أطراف العقد</t>
+          <t>غياب الشهود في عقد البيع العقاري</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 2</t>
+          <t>م.ع.ع الفصل 472</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1373,27 +1373,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R_GEN_003</t>
+          <t>R_WD_003</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>عام</t>
+          <t>وعد بالبيع</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>تحديد موضوع العقد بوضوح</t>
+          <t>تحديد قيمة العربون وشروط استرجاعه</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>موضوع العقد غامض أو ناقص</t>
+          <t>غياب شروط استرجاع العربون</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 5</t>
+          <t>م.ع.ع الفصل 439-441</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>بطلان — موضوع مجهول</t>
+          <t>نزاع حول العربون عند التراجع</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1481,7 +1481,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R_KR_007</t>
+          <t>R_KR_003</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1491,17 +1491,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>منع التسويغ الفرعي</t>
+          <t>الإشعار المسبق بالخروج</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>غياب بند حظر التسويغ للغير</t>
+          <t>غياب بند الإشعار المسبق</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 770</t>
+          <t>م.ع.ع الفصل 766 / قانون 1977</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>خطر تسويغ فرعي غير مشروع</t>
+          <t>تعويض شهر كراء كامل</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1535,7 +1535,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R_KR_005</t>
+          <t>R_KR_004</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>بند الفسخ والجزاء</t>
+          <t>بند الكفالة/الضمان</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>غياب بند الفسخ الوجوبي</t>
+          <t>غياب بند الضمان في عقد الكراء</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 273</t>
+          <t>م.ع.ع الفصل 1478</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>تعقيد الإجراءات القضائية للإخلاء</t>
+          <t>خطر مالي — لا ضمان عند الإخلال</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1589,27 +1589,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R_GEN_004</t>
+          <t>R_KR_005</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>عام</t>
+          <t>كراء</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>كتابة العقد بلغة واضحة</t>
+          <t>بند الفسخ والجزاء</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>عقد غامض أو متناقض في بنوده</t>
+          <t>غياب بند الفسخ الوجوبي</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 543</t>
+          <t>م.ع.ع الفصل 273</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>تأويل ضد الطرف الذي حرر العقد</t>
+          <t>تعقيد الإجراءات القضائية للإخلاء</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1643,27 +1643,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R_KR_004</t>
+          <t>R_GEN_004</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>كراء</t>
+          <t>عام</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>بند الكفالة/الضمان</t>
+          <t>كتابة العقد بلغة واضحة</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>غياب بند الضمان في عقد الكراء</t>
+          <t>عقد غامض أو متناقض في بنوده</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 1478</t>
+          <t>م.ع.ع الفصل 543</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>خطر مالي — لا ضمان عند الإخلال</t>
+          <t>تأويل ضد الطرف الذي حرر العقد</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1697,7 +1697,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R_KR_003</t>
+          <t>R_KR_007</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>الإشعار المسبق بالخروج</t>
+          <t>منع التسويغ الفرعي</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>غياب بند الإشعار المسبق</t>
+          <t>غياب بند حظر التسويغ للغير</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>م.ع.ع الفصل 766 / قانون 1977</t>
+          <t>م.ع.ع الفصل 770</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>تعويض شهر كراء كامل</t>
+          <t>خطر تسويغ فرعي غير مشروع</t>
         </is>
       </c>
       <c r="H24" t="n">
